--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +43,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004F1A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -640,8 +649,6 @@
           <t>https://complex.ba</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>72</t>
@@ -687,8 +694,6 @@
           <t>https://www.instagram.com/complex_bih/</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Almir Hadziosmanovic</t>
@@ -699,8 +704,6 @@
           <t>General Manager</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/almir-hadziosmanovic-a7a97b24b</t>
@@ -753,8 +756,6 @@
           <t>https://complex.ba</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>72</t>
@@ -800,8 +801,6 @@
           <t>https://www.instagram.com/complex_bih/</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Alma Lisakovic</t>
@@ -812,9 +811,233 @@
           <t>Import Manager</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alma-lisakovic-527820234/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Almir Hadziosmanovic</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/almir-hadziosmanovic-a7a97b24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Alma Lisakovic</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alma-lisakovic-527820234/</t>
         </is>

--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1043,6 +1043,232 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Almir Hadziosmanovic</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/almir-hadziosmanovic-a7a97b24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Alma Lisakovic</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alma-lisakovic-527820234/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1269,6 +1269,232 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Almir Hadziosmanovic</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/almir-hadziosmanovic-a7a97b24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Complex D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>146481</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>bb Krivoglavci I</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://complex.ba</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>almir@complex.ba</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 273-800</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>4201136260006</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/complex-doo/</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/complex.ba/</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/complex_bih/</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Alma Lisakovic</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alma-lisakovic-527820234/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1495,6 +1495,115 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Međugorje</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Hercegovačko-neretvanski kanton</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Gospodarska zona, Tromeđa VI br.7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88266</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://union-foods.com</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>info@union-foods.com</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>+387 36 653-450</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4227040010008</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unionfoodsdoo</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/union_foods/</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/unionfoods</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Ilija Barbaric</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilija-barbaric-1137a43a/?originalSubdomain=ba</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1604,6 +1604,115 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Međugorje</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Hercegovačko-neretvanski kanton</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Gospodarska zona, Tromeđa VI br.7</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88266</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://union-foods.com</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>info@union-foods.com</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>+387 36 653-450</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>4227040010008</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unionfoodsdoo</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/union_foods/</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/unionfoods</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Ilija Barbaric</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilija-barbaric-1137a43a/?originalSubdomain=ba</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1713,6 +1713,115 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Međugorje</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Hercegovačko-neretvanski kanton</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Gospodarska zona, Tromeđa VI br.7</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>88266</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://union-foods.com</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>info@union-foods.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>+387 36 653-450</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>4227040010008</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unionfoodsdoo</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/union_foods/</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/unionfoods</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Ilija Barbaric</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilija-barbaric-1137a43a/?originalSubdomain=ba</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
